--- a/test_data/icpms_test/Test_Data_Results.xlsx
+++ b/test_data/icpms_test/Test_Data_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimbo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Daven/Projects/Sparrow/Labs/Sparrow-CU-TRaIL/test_data/icpms_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E8C3B3-8355-0F42-8C32-1F78AFB8A6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7AB01A-9B4F-8545-AEE3-50C828E3A04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="500" windowWidth="52540" windowHeight="30540" xr2:uid="{AB9FA966-99FF-A742-8C7A-DCACFBC5B889}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="25880" windowHeight="21580" xr2:uid="{AB9FA966-99FF-A742-8C7A-DCACFBC5B889}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -224,15 +224,9 @@
     <t>UnCorr Ft 235U</t>
   </si>
   <si>
-    <t>UnCorrFt 232Th</t>
-  </si>
-  <si>
     <t>UnCorr Ft 147Sm</t>
   </si>
   <si>
-    <t>GeoCorrFt 238U</t>
-  </si>
-  <si>
     <t>GeoCorr Ft 235U</t>
   </si>
   <si>
@@ -249,6 +243,12 @@
   </si>
   <si>
     <t>z</t>
+  </si>
+  <si>
+    <t>GeoCorr Ft 238U</t>
+  </si>
+  <si>
+    <t>UnCorr Ft 232Th</t>
   </si>
 </sst>
 </file>
@@ -689,7 +689,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -782,23 +782,23 @@
         <v>61</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.2">
@@ -818,7 +818,7 @@
         <v>139.02000000000001</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>25</v>
@@ -947,7 +947,7 @@
         <v>149.41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>25</v>
@@ -1076,7 +1076,7 @@
         <v>143.18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>25</v>
@@ -1205,7 +1205,7 @@
         <v>80.510000000000005</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>25</v>
@@ -1334,7 +1334,7 @@
         <v>276.64999999999998</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>25</v>
@@ -1463,7 +1463,7 @@
         <v>102.6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>25</v>
@@ -1592,7 +1592,7 @@
         <v>61.3</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>25</v>
@@ -1721,7 +1721,7 @@
         <v>60.2</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>25</v>
@@ -1850,7 +1850,7 @@
         <v>89.5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>25</v>
@@ -1979,7 +1979,7 @@
         <v>74.599999999999994</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>25</v>
@@ -2108,7 +2108,7 @@
         <v>102.02</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>25</v>
@@ -2237,7 +2237,7 @@
         <v>114.5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
@@ -2366,7 +2366,7 @@
         <v>120.6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>25</v>
@@ -2495,7 +2495,7 @@
         <v>148</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>25</v>
@@ -2624,7 +2624,7 @@
         <v>124.6</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>25</v>
@@ -2753,7 +2753,7 @@
         <v>86.9</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>25</v>
@@ -2882,7 +2882,7 @@
         <v>214</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>25</v>
@@ -3011,7 +3011,7 @@
         <v>143</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>25</v>
@@ -3140,7 +3140,7 @@
         <v>160.5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>25</v>
@@ -3269,7 +3269,7 @@
         <v>195.8</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>25</v>
@@ -3398,7 +3398,7 @@
         <v>102.8</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>25</v>
@@ -3527,7 +3527,7 @@
         <v>119.9</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>25</v>
@@ -3656,7 +3656,7 @@
         <v>89.8</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>25</v>
@@ -3785,7 +3785,7 @@
         <v>130.9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>25</v>
@@ -3914,7 +3914,7 @@
         <v>123.5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>25</v>
@@ -4043,7 +4043,7 @@
         <v>110</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>52</v>
@@ -4172,7 +4172,7 @@
         <v>131</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>52</v>
@@ -4301,7 +4301,7 @@
         <v>91</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>52</v>
@@ -4430,7 +4430,7 @@
         <v>201</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>52</v>
@@ -4559,7 +4559,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>52</v>
@@ -4688,7 +4688,7 @@
         <v>151</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>52</v>
